--- a/data/raw/企业名单.xlsx
+++ b/data/raw/企业名单.xlsx
@@ -2,16 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
   <bookViews>
     <workbookView windowWidth="21600" windowHeight="10620"/>
   </bookViews>
   <sheets>
-    <sheet name="企业名单" sheetId="2" r:id="rId1"/>
+    <sheet name="企业名单" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">企业名单!$A$1:$B$642</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,19 +38,19 @@
     <t>保证人</t>
   </si>
   <si>
-    <t>安宁固收B0009号</t>
+    <t>ANGS-B0009</t>
   </si>
   <si>
     <t>杭州钱塘新区建设投资集团有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0010号</t>
+    <t>ANGS-B0010</t>
   </si>
   <si>
     <t>诸暨市国有资产经营有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0011号</t>
+    <t>ANGS-B0011</t>
   </si>
   <si>
     <t>杭州东部城市建设投资集团有限公司</t>
@@ -62,16 +59,16 @@
     <t>杭州钱塘新区城市发展集团有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0012号</t>
+    <t>ANGS-B0012</t>
   </si>
   <si>
     <t>桐庐县国有资本投资运营控股集团有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0014号</t>
-  </si>
-  <si>
-    <t>安宁固收B0015号</t>
+    <t>ANGS-B0014</t>
+  </si>
+  <si>
+    <t>ANGS-B0015</t>
   </si>
   <si>
     <t>嵊州市交通投资发展集团有限公司</t>
@@ -80,94 +77,94 @@
     <t>嵊州市投资控股有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0018号</t>
-  </si>
-  <si>
-    <t>安宁固收B0020号</t>
+    <t>ANGS-B0018</t>
+  </si>
+  <si>
+    <t>ANGS-B0020</t>
   </si>
   <si>
     <t>诸暨市建设集团有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0021号</t>
+    <t>ANGS-B0021</t>
   </si>
   <si>
     <t>诸暨市城乡投资集团有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0022号</t>
+    <t>ANGS-B0022</t>
   </si>
   <si>
     <t>嵊州市市场发展有限公司</t>
   </si>
   <si>
-    <t>安宁固收B0023号</t>
-  </si>
-  <si>
-    <t>安宁固收B0024号</t>
-  </si>
-  <si>
-    <t>安盈固收T0001号</t>
+    <t>ANGS-B0023</t>
+  </si>
+  <si>
+    <t>ANGS-B0024</t>
+  </si>
+  <si>
+    <t>AYGS-T0001</t>
   </si>
   <si>
     <t>浦江县国有资本投资集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0004号</t>
+    <t>AYGS-T0004</t>
   </si>
   <si>
     <t>杭州之江城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0005号</t>
-  </si>
-  <si>
-    <t>安盈固收T0006号</t>
-  </si>
-  <si>
-    <t>安盈固收T0021号</t>
+    <t>AYGS-T0005</t>
+  </si>
+  <si>
+    <t>AYGS-T0006</t>
+  </si>
+  <si>
+    <t>AYGS-T0021</t>
   </si>
   <si>
     <t>宁波市奉化区三高铁路投资有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0022号</t>
+    <t>AYGS-T0022</t>
   </si>
   <si>
     <t>丽水南城新区投资发展有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0023号</t>
+    <t>AYGS-T0023</t>
   </si>
   <si>
     <t>深圳市罗湖城市发展有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0024号</t>
+    <t>AYGS-T0024</t>
   </si>
   <si>
     <t>遂昌县建设投资发展有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0026号</t>
+    <t>AYGS-T0026</t>
   </si>
   <si>
     <t>浙江余杭经济开发区投资有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0029号</t>
+    <t>AYGS-T0029</t>
   </si>
   <si>
     <t>东阳市交通投资建设集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0041号</t>
+    <t>AYGS-T0041</t>
   </si>
   <si>
     <t>浙江湘旅控股集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0042号</t>
+    <t>AYGS-T0042</t>
   </si>
   <si>
     <t>丽水莲都城乡产业投资发展集团有限公司</t>
@@ -176,13 +173,13 @@
     <t>丽水市莲都区国有资本运营有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0046号</t>
+    <t>AYGS-T0046</t>
   </si>
   <si>
     <t>北京市谷财集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0050号</t>
+    <t>AYGS-T0050</t>
   </si>
   <si>
     <t>嘉兴经济技术开发区建设投资集团有限公司</t>
@@ -191,7 +188,7 @@
     <t>嘉兴国际商务区投资建设集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0053号</t>
+    <t>AYGS-T0053</t>
   </si>
   <si>
     <t>青田县国有资产控股集团有限公司</t>
@@ -200,7 +197,7 @@
     <t>青田县交通发展投资有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0056号</t>
+    <t>AYGS-T0056</t>
   </si>
   <si>
     <t>杭州良渚文化城集团有限公司</t>
@@ -209,10 +206,10 @@
     <t>杭州余杭国有资本投资运营集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0057号</t>
-  </si>
-  <si>
-    <t>安盈固收T0058号</t>
+    <t>AYGS-T0057</t>
+  </si>
+  <si>
+    <t>AYGS-T0058</t>
   </si>
   <si>
     <t>云和县富云国有资产投资集团有限公司</t>
@@ -221,25 +218,25 @@
     <t>云和县国有资本运营有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0059号</t>
+    <t>AYGS-T0059</t>
   </si>
   <si>
     <t>东阳市城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0061号</t>
+    <t>AYGS-T0061</t>
   </si>
   <si>
     <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0062号</t>
+    <t>AYGS-T0062</t>
   </si>
   <si>
     <t>东阳市城市发展集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0063号</t>
+    <t>AYGS-T0063</t>
   </si>
   <si>
     <t>建德经开投资发展有限公司</t>
@@ -248,7 +245,7 @@
     <t>建德市国有资产经营有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0064号</t>
+    <t>AYGS-T0064</t>
   </si>
   <si>
     <t>兰溪市城市投资集团有限公司</t>
@@ -257,16 +254,16 @@
     <t>兰溪市兰创投资集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0066号</t>
+    <t>AYGS-T0066</t>
   </si>
   <si>
     <t>杭州余杭城市发展投资集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0067号</t>
-  </si>
-  <si>
-    <t>安盈固收T0079号</t>
+    <t>AYGS-T0067</t>
+  </si>
+  <si>
+    <t>AYGS-T0079</t>
   </si>
   <si>
     <t>宁波宁南新城开发投资有限公司</t>
@@ -275,7 +272,7 @@
     <t>宁波宁南新城国有资产经营管理有限责任公司</t>
   </si>
   <si>
-    <t>安盈固收T0080号</t>
+    <t>AYGS-T0080</t>
   </si>
   <si>
     <t>金华金开国有资本投资有限公司</t>
@@ -284,7 +281,7 @@
     <t>金华金开文化旅游发展集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0081号</t>
+    <t>AYGS-T0081</t>
   </si>
   <si>
     <t>舟山市定海区城市建设投资开发有限公司</t>
@@ -293,10 +290,10 @@
     <t>舟山市定海区城乡建设集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0082号</t>
-  </si>
-  <si>
-    <t>安盈固收T0083号</t>
+    <t>AYGS-T0082</t>
+  </si>
+  <si>
+    <t>AYGS-T0083</t>
   </si>
   <si>
     <t>绍兴袍江控股集团有限公司</t>
@@ -305,13 +302,13 @@
     <t>绍兴高新技术产业开发区投资发展集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0084号</t>
+    <t>AYGS-T0084</t>
   </si>
   <si>
     <t>丽水经济技术开发区实业发展集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0085号</t>
+    <t>AYGS-T0085</t>
   </si>
   <si>
     <t>海宁仰山实业集团有限公司</t>
@@ -320,13 +317,13 @@
     <t>浙江杭海新城控股集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0086号</t>
+    <t>AYGS-T0086</t>
   </si>
   <si>
     <t>青田县城市发展投资有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0092号</t>
+    <t>AYGS-T0092</t>
   </si>
   <si>
     <t>舟山市普陀交通旅游集团有限公司</t>
@@ -335,13 +332,13 @@
     <t>舟山市普陀区国有资产投资经营有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0093号</t>
+    <t>AYGS-T0093</t>
   </si>
   <si>
     <t>北京昌平科技园发展集团有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0111号</t>
+    <t>AYGS-T0111</t>
   </si>
   <si>
     <t>宁波梅山岛开发投资有限公司</t>
@@ -350,22 +347,22 @@
     <t>宁波梅山保税港区物流有限公司</t>
   </si>
   <si>
-    <t>安盈固收T0112号</t>
-  </si>
-  <si>
-    <t>安盈固收T0113号</t>
+    <t>AYGS-T0112</t>
+  </si>
+  <si>
+    <t>AYGS-T0113</t>
   </si>
   <si>
     <t>北京广安控股集团有限公司</t>
   </si>
   <si>
-    <t>成都华兴其他行政管理服务信托</t>
+    <t>CDHX</t>
   </si>
   <si>
     <t>成都市华兴住宅房地产开发有限公司</t>
   </si>
   <si>
-    <t>鼎新增益6号</t>
+    <t>DXZY-6</t>
   </si>
   <si>
     <t>成都温江兴蓉西城市运营集团有限公司</t>
@@ -383,25 +380,25 @@
     <t>宜昌城发城市运营有限公司</t>
   </si>
   <si>
-    <t>丰产添益3号</t>
+    <t>FCTY-3</t>
   </si>
   <si>
     <t>北京市通州区国有资本运营有限公司</t>
   </si>
   <si>
-    <t>丰产添益4号</t>
+    <t>FCTY-4</t>
   </si>
   <si>
     <t>扬州广合国有资本运营集团有限公司</t>
   </si>
   <si>
-    <t>丰产添益52号</t>
+    <t>FCTY-52</t>
   </si>
   <si>
     <t>绍兴袍江新农村建设投资有限公司</t>
   </si>
   <si>
-    <t>丰产添益53号</t>
+    <t>FCTY-53</t>
   </si>
   <si>
     <t>湖州南浔文旅发展集团有限公司</t>
@@ -410,7 +407,7 @@
     <t>湖州南浔旅游投资发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产添益54号</t>
+    <t>FCTY-54</t>
   </si>
   <si>
     <t>浙江南太湖城市开发控股集团有限公司</t>
@@ -419,34 +416,34 @@
     <t>湖州南太湖国有控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产添益5号</t>
-  </si>
-  <si>
-    <t>丰产添益6号</t>
-  </si>
-  <si>
-    <t>丰产添益7号</t>
+    <t>FCTY-5</t>
+  </si>
+  <si>
+    <t>FCTY-6</t>
+  </si>
+  <si>
+    <t>FCTY-7</t>
   </si>
   <si>
     <t>绍兴袍江创业建设发展有限公司</t>
   </si>
   <si>
-    <t>丰产添益8号</t>
-  </si>
-  <si>
-    <t>丰产添益9号</t>
+    <t>FCTY-8</t>
+  </si>
+  <si>
+    <t>FCTY-9</t>
   </si>
   <si>
     <t>兰溪市国有资本运营集团有限公司</t>
   </si>
   <si>
-    <t>丰产投管10号</t>
-  </si>
-  <si>
-    <t>丰产投管11号</t>
-  </si>
-  <si>
-    <t>丰产投管1号</t>
+    <t>FCTG-10</t>
+  </si>
+  <si>
+    <t>FCTG-11</t>
+  </si>
+  <si>
+    <t>FCTG-1</t>
   </si>
   <si>
     <t>湖北澴川国有资本投资运营集团有限公司</t>
@@ -458,10 +455,10 @@
     <t>池州市投资控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产投管2号</t>
-  </si>
-  <si>
-    <t>丰产投配1号</t>
+    <t>FCTG-2</t>
+  </si>
+  <si>
+    <t>FCTP-1</t>
   </si>
   <si>
     <t>重庆市涪陵实业发展集团有限公司</t>
@@ -470,109 +467,109 @@
     <t>成都空港产业兴城投资发展有限公司</t>
   </si>
   <si>
-    <t>丰产投配2号</t>
+    <t>FCTP-2</t>
   </si>
   <si>
     <t>成都香城产业发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产投配3号</t>
+    <t>FCTP-3</t>
   </si>
   <si>
     <t>成都香城投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产投配4号</t>
-  </si>
-  <si>
-    <t>丰产投配5号</t>
-  </si>
-  <si>
-    <t>丰产投配6号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管104号</t>
+    <t>FCTP-4</t>
+  </si>
+  <si>
+    <t>FCTP-5</t>
+  </si>
+  <si>
+    <t>FCTP-6</t>
+  </si>
+  <si>
+    <t>FCZS-TG104</t>
   </si>
   <si>
     <t>盐城市国能投资有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管106号</t>
+    <t>FCZS-TG106</t>
   </si>
   <si>
     <t>长兴交通投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管109号</t>
+    <t>FCZS-TG109</t>
   </si>
   <si>
     <t>绍兴市柯桥区轨道交通集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管113号</t>
+    <t>FCZS-TG113</t>
   </si>
   <si>
     <t>肇庆新区投资发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管124号</t>
+    <t>FCZS-TG124</t>
   </si>
   <si>
     <t>淮安市开控实业投资发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管127号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管135号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管136号</t>
+    <t>FCZS-TG127</t>
+  </si>
+  <si>
+    <t>FCZS-TG135</t>
+  </si>
+  <si>
+    <t>FCZS-TG136</t>
   </si>
   <si>
     <t>余姚市姚北物产有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管139号</t>
+    <t>FCZS-TG139</t>
   </si>
   <si>
     <t>台州市路桥区社会事业发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管13号</t>
+    <t>FCZS-TG13</t>
   </si>
   <si>
     <t>漳州市交通发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管140号</t>
+    <t>FCZS-TG140</t>
   </si>
   <si>
     <t>淮安兴盛建设投资有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管162号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管167号</t>
+    <t>FCZS-TG162</t>
+  </si>
+  <si>
+    <t>FCZS-TG167</t>
   </si>
   <si>
     <t>淮安国控投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管16号</t>
+    <t>FCZS-TG16</t>
   </si>
   <si>
     <t>赣州旅游投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管170号</t>
+    <t>FCZS-TG170</t>
   </si>
   <si>
     <t>江苏盐城港大丰港开发集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管175号</t>
+    <t>FCZS-TG175</t>
   </si>
   <si>
     <t>淮安高新控股有限公司</t>
@@ -581,28 +578,28 @@
     <t>淮安市国联城市运营管理有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管180号</t>
+    <t>FCZS-TG180</t>
   </si>
   <si>
     <t>江苏金海投资有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管189号</t>
+    <t>FCZS-TG189</t>
   </si>
   <si>
     <t>泰州东部新城控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管20号</t>
+    <t>FCZS-TG20</t>
   </si>
   <si>
     <t>常德市城市发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管212号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管224号</t>
+    <t>FCZS-TG212</t>
+  </si>
+  <si>
+    <t>FCZS-TG224</t>
   </si>
   <si>
     <t>泰州医药城控股集团有限公司</t>
@@ -611,10 +608,10 @@
     <t>江苏创鸿控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管233号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管243号</t>
+    <t>FCZS-TG233</t>
+  </si>
+  <si>
+    <t>FCZS-TG243</t>
   </si>
   <si>
     <t>泰州市凯明城市建设有限公司</t>
@@ -623,25 +620,25 @@
     <t>泰州国控投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管246号</t>
+    <t>FCZS-TG246</t>
   </si>
   <si>
     <t>盐城高新区投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管254号</t>
+    <t>FCZS-TG254</t>
   </si>
   <si>
     <t>浙江长兴国有资产投资控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管257号</t>
+    <t>FCZS-TG257</t>
   </si>
   <si>
     <t>盐城市都市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管264号</t>
+    <t>FCZS-TG264</t>
   </si>
   <si>
     <t>盐城市水务集团有限公司</t>
@@ -650,82 +647,82 @@
     <t>盐城市交通投资建设控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管4号</t>
+    <t>FCZS-TG4</t>
   </si>
   <si>
     <t>成都空港产融投资发展有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管65号</t>
+    <t>FCZS-TG65</t>
   </si>
   <si>
     <t>湖北三峡文化旅游集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管71号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管72号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管75号</t>
+    <t>FCZS-TG71</t>
+  </si>
+  <si>
+    <t>FCZS-TG72</t>
+  </si>
+  <si>
+    <t>FCZS-TG75</t>
   </si>
   <si>
     <t>扬州新城国有资产投资发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管79号</t>
+    <t>FCZS-TG79</t>
   </si>
   <si>
     <t>衢州工业发展集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管7号</t>
+    <t>FCZS-TG7</t>
   </si>
   <si>
     <t>诸暨市交通基础设施建设有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管81号</t>
+    <t>FCZS-TG81</t>
   </si>
   <si>
     <t>绍兴市柯桥区建设集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管89号</t>
-  </si>
-  <si>
-    <t>丰产增收-投管96号</t>
+    <t>FCZS-TG89</t>
+  </si>
+  <si>
+    <t>FCZS-TG96</t>
   </si>
   <si>
     <t>衡阳高新控股集团有限公司</t>
   </si>
   <si>
-    <t>丰产增收-投管9号</t>
+    <t>FCZS-TG9</t>
   </si>
   <si>
     <t>上饶市城市运营（控股）集团有限公司</t>
   </si>
   <si>
-    <t>华夏幸福九通基业</t>
+    <t>JTJY</t>
   </si>
   <si>
     <t>九通基业投资有限公司</t>
   </si>
   <si>
-    <t>嘉园165号</t>
+    <t>JY-165</t>
   </si>
   <si>
     <t>天津房地产集团有限公司</t>
   </si>
   <si>
-    <t>嘉园285号</t>
+    <t>JY-285</t>
   </si>
   <si>
     <t>天津博雅置业有限公司</t>
   </si>
   <si>
-    <t>嘉园378号</t>
+    <t>JY-378</t>
   </si>
   <si>
     <t>武汉名流时代置业有限公司</t>
@@ -734,352 +731,352 @@
     <t>四川蓝光发展股份有限公司</t>
   </si>
   <si>
-    <t>嘉园439号</t>
+    <t>JY-439</t>
   </si>
   <si>
     <t>广东奥园商业地产集团有限公司</t>
   </si>
   <si>
-    <t>嘉园632号</t>
+    <t>JY-632</t>
   </si>
   <si>
     <t>新世界中国地产（海口）有限公司</t>
   </si>
   <si>
-    <t>嘉园828号</t>
+    <t>JY-828</t>
   </si>
   <si>
     <t>陕西金泰恒业房地产有限公司</t>
   </si>
   <si>
-    <t>嘉园850号</t>
+    <t>JY-850</t>
   </si>
   <si>
     <t>上海远星寰宇房地产集团有限公司</t>
   </si>
   <si>
-    <t>嘉园922号</t>
+    <t>JY-922</t>
   </si>
   <si>
     <t>成都兴城人居地产投资集团股份有限公司</t>
   </si>
   <si>
-    <t>京投公司</t>
+    <t>JTGS</t>
   </si>
   <si>
     <t>北京市基础设施投资有限公司（原北京地铁集团有限责任公司）</t>
   </si>
   <si>
-    <t>聚通343号</t>
+    <t>JT-343</t>
   </si>
   <si>
     <t>海尔集团（青岛）金盈控股有限公司</t>
   </si>
   <si>
-    <t>聚通357号</t>
+    <t>JT-357</t>
   </si>
   <si>
     <t>上海国有资本投资有限公司</t>
   </si>
   <si>
-    <t>聚通365号</t>
+    <t>JT-365</t>
   </si>
   <si>
     <t>新奥科技发展有限公司</t>
   </si>
   <si>
-    <t>聚通367号</t>
+    <t>JT-367</t>
   </si>
   <si>
     <t>平安点创国际融资租赁有限公司</t>
   </si>
   <si>
-    <t>聚通373号</t>
+    <t>JT-373</t>
   </si>
   <si>
     <t>北京北辰实业集团有限责任公司</t>
   </si>
   <si>
-    <t>聚通376号</t>
+    <t>JT-376</t>
   </si>
   <si>
     <t>北京市东郊农场有限公司</t>
   </si>
   <si>
-    <t>聚通379号</t>
+    <t>JT-379</t>
   </si>
   <si>
     <t>国轩高科股份有限公司</t>
   </si>
   <si>
-    <t>聚通381号</t>
+    <t>JT-381</t>
   </si>
   <si>
     <t>厦门象屿金象控股集团有限公司</t>
   </si>
   <si>
-    <t>聚通382号</t>
+    <t>JT-382</t>
   </si>
   <si>
     <t>台州市南部湾区投资集团有限公司</t>
   </si>
   <si>
-    <t>聚通392号</t>
+    <t>JT-392</t>
   </si>
   <si>
     <t>新奥控股投资股份有限公司</t>
   </si>
   <si>
-    <t>聚通405号</t>
-  </si>
-  <si>
-    <t>聚通412号</t>
+    <t>JT-405</t>
+  </si>
+  <si>
+    <t>JT-412</t>
   </si>
   <si>
     <t>海发宝诚融资租赁有限公司</t>
   </si>
   <si>
-    <t>聚通415号</t>
+    <t>JT-415</t>
   </si>
   <si>
     <t>海尔融资租赁股份有限公司</t>
   </si>
   <si>
-    <t>聚通418号</t>
-  </si>
-  <si>
-    <t>蓝色鑫源2号</t>
+    <t>JT-418</t>
+  </si>
+  <si>
+    <t>LSXY-2</t>
   </si>
   <si>
     <t>上海畅途融资租赁有限公司</t>
   </si>
   <si>
-    <t>融诚1014号</t>
+    <t>RC-1014</t>
   </si>
   <si>
     <t>无锡市滨湖国有资产运营（集团）有限公司</t>
   </si>
   <si>
-    <t>融诚1020号</t>
+    <t>RC-1020</t>
   </si>
   <si>
     <t>宁波慈溪城建投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1023号</t>
+    <t>RC-1023</t>
   </si>
   <si>
     <t>济南城市投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1027号</t>
+    <t>RC-1027</t>
   </si>
   <si>
     <t>杭州西湖城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1037号</t>
+    <t>RC-1037</t>
   </si>
   <si>
     <t>四会市国有资产经营有限公司</t>
   </si>
   <si>
-    <t>融诚1038号</t>
-  </si>
-  <si>
-    <t>融诚1041号</t>
+    <t>RC-1038</t>
+  </si>
+  <si>
+    <t>RC-1041</t>
   </si>
   <si>
     <t>南京吉山国有资产运营集团有限公司</t>
   </si>
   <si>
-    <t>融诚1042号</t>
+    <t>RC-1042</t>
   </si>
   <si>
     <t>龙港市城市建设发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1043号</t>
+    <t>RC-1043</t>
   </si>
   <si>
     <t>盐城市国有资产投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1045号</t>
+    <t>RC-1045</t>
   </si>
   <si>
     <t>浙江瓯海产业投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1050号</t>
+    <t>RC-1050</t>
   </si>
   <si>
     <t>遂昌县国有资本投资运营集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚1051号</t>
-  </si>
-  <si>
-    <t>融诚1052号</t>
+    <t>RC-1051</t>
+  </si>
+  <si>
+    <t>RC-1052</t>
   </si>
   <si>
     <t>青田经济开发区投资发展有限公司</t>
   </si>
   <si>
-    <t>融诚1061号</t>
+    <t>RC-1061</t>
   </si>
   <si>
     <t>福建漳州城投集团有限公司</t>
   </si>
   <si>
-    <t>融诚1062号</t>
+    <t>RC-1062</t>
   </si>
   <si>
     <t>河南航空港投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1063号</t>
+    <t>RC-1063</t>
   </si>
   <si>
     <t>济南城市建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚1069号</t>
+    <t>RC-1069</t>
   </si>
   <si>
     <t>合肥新站科技产业发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1070号</t>
+    <t>RC-1070</t>
   </si>
   <si>
     <t>合肥市东鑫建设投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1071号</t>
-  </si>
-  <si>
-    <t>融诚1072号</t>
+    <t>RC-1071</t>
+  </si>
+  <si>
+    <t>RC-1072</t>
   </si>
   <si>
     <t>巢湖市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1074号</t>
-  </si>
-  <si>
-    <t>融诚1076号</t>
+    <t>RC-1074</t>
+  </si>
+  <si>
+    <t>RC-1076</t>
   </si>
   <si>
     <t>山东省财金投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1078号</t>
+    <t>RC-1078</t>
   </si>
   <si>
     <t>桐庐西部开发建设有限公司</t>
   </si>
   <si>
-    <t>融诚1079号</t>
-  </si>
-  <si>
-    <t>融诚1082号</t>
+    <t>RC-1079</t>
+  </si>
+  <si>
+    <t>RC-1082</t>
   </si>
   <si>
     <t>靖江市北辰城乡投资建设有限公司</t>
   </si>
   <si>
-    <t>融诚1088号</t>
+    <t>RC-1088</t>
   </si>
   <si>
     <t>浙江省岱山经济开发区环城投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1089号</t>
+    <t>RC-1089</t>
   </si>
   <si>
     <t>武汉市公共交通集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚1093号</t>
+    <t>RC-1093</t>
   </si>
   <si>
     <t>东阳市国有资产投资有限公司</t>
   </si>
   <si>
-    <t>融诚1094号</t>
-  </si>
-  <si>
-    <t>融诚1097号</t>
+    <t>RC-1094</t>
+  </si>
+  <si>
+    <t>RC-1097</t>
   </si>
   <si>
     <t>绍兴市越城区城市发展建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚1100号</t>
+    <t>RC-1100</t>
   </si>
   <si>
     <t>江山经济开发区建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1101号</t>
+    <t>RC-1101</t>
   </si>
   <si>
     <t>湖北宏泰集团有限公司</t>
   </si>
   <si>
-    <t>融诚1102号</t>
-  </si>
-  <si>
-    <t>融诚1103号</t>
+    <t>RC-1102</t>
+  </si>
+  <si>
+    <t>RC-1103</t>
   </si>
   <si>
     <t>西安经发控股(集团)有限责任公司</t>
   </si>
   <si>
-    <t>融诚1104号</t>
+    <t>RC-1104</t>
   </si>
   <si>
     <t>惠州仲恺城市发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1105号</t>
-  </si>
-  <si>
-    <t>融诚1106号</t>
-  </si>
-  <si>
-    <t>融诚1110号</t>
-  </si>
-  <si>
-    <t>融诚1115号</t>
+    <t>RC-1105</t>
+  </si>
+  <si>
+    <t>RC-1106</t>
+  </si>
+  <si>
+    <t>RC-1110</t>
+  </si>
+  <si>
+    <t>RC-1115</t>
   </si>
   <si>
     <t>嘉兴市秀湖发展投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1116号</t>
-  </si>
-  <si>
-    <t>融诚1120号</t>
-  </si>
-  <si>
-    <t>融诚1123号</t>
-  </si>
-  <si>
-    <t>融诚1125号</t>
+    <t>RC-1116</t>
+  </si>
+  <si>
+    <t>RC-1120</t>
+  </si>
+  <si>
+    <t>RC-1123</t>
+  </si>
+  <si>
+    <t>RC-1125</t>
   </si>
   <si>
     <t>江苏淮阴城市产业投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1126号</t>
+    <t>RC-1126</t>
   </si>
   <si>
     <t>宁波市镇海区海江投资发展有限公司</t>
   </si>
   <si>
-    <t>融诚1127号</t>
+    <t>RC-1127</t>
   </si>
   <si>
     <t>浙江湖州南浔经济建设开发有限公司</t>
@@ -1088,37 +1085,37 @@
     <t>湖州南浔新开建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚1128号</t>
+    <t>RC-1128</t>
   </si>
   <si>
     <t>乐山国有资产投资运营（集团）有限公司</t>
   </si>
   <si>
-    <t>融诚1129号</t>
-  </si>
-  <si>
-    <t>融诚1131号</t>
+    <t>RC-1129</t>
+  </si>
+  <si>
+    <t>RC-1131</t>
   </si>
   <si>
     <t>九江市国有投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1133号</t>
-  </si>
-  <si>
-    <t>融诚1134号</t>
-  </si>
-  <si>
-    <t>融诚1139号</t>
-  </si>
-  <si>
-    <t>融诚1142号</t>
+    <t>RC-1133</t>
+  </si>
+  <si>
+    <t>RC-1134</t>
+  </si>
+  <si>
+    <t>RC-1139</t>
+  </si>
+  <si>
+    <t>RC-1142</t>
   </si>
   <si>
     <t>漳州市九龙江集团有限公司</t>
   </si>
   <si>
-    <t>融诚1145号</t>
+    <t>RC-1145</t>
   </si>
   <si>
     <t>浙江岭发控股有限公司</t>
@@ -1127,94 +1124,94 @@
     <t>温岭市国有资产投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1150号</t>
+    <t>RC-1150</t>
   </si>
   <si>
     <t>宁波象港开发控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1152号</t>
-  </si>
-  <si>
-    <t>融诚1159号</t>
-  </si>
-  <si>
-    <t>融诚1162号</t>
+    <t>RC-1152</t>
+  </si>
+  <si>
+    <t>RC-1159</t>
+  </si>
+  <si>
+    <t>RC-1162</t>
   </si>
   <si>
     <t>长沙市芙蓉城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1165号</t>
+    <t>RC-1165</t>
   </si>
   <si>
     <t>湖北省资产管理有限公司</t>
   </si>
   <si>
-    <t>融诚1173号</t>
+    <t>RC-1173</t>
   </si>
   <si>
     <t>泰州凤城河建设发展有限公司</t>
   </si>
   <si>
-    <t>融诚1180号</t>
+    <t>RC-1180</t>
   </si>
   <si>
     <t>武汉新能实业发展有限公司</t>
   </si>
   <si>
-    <t>融诚1184号</t>
+    <t>RC-1184</t>
   </si>
   <si>
     <t>衢州市国有资本运营有限公司</t>
   </si>
   <si>
-    <t>融诚1185号</t>
+    <t>RC-1185</t>
   </si>
   <si>
     <t>株洲市国有资产投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1186号</t>
+    <t>RC-1186</t>
   </si>
   <si>
     <t>亳州市产业资本投资运营控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1193号</t>
+    <t>RC-1193</t>
   </si>
   <si>
     <t>乌鲁木齐经济技术开发区建发国有资本投资运营（集团）有限公司</t>
   </si>
   <si>
-    <t>融诚1198号</t>
+    <t>RC-1198</t>
   </si>
   <si>
     <t>同安控股有限责任公司</t>
   </si>
   <si>
-    <t>融诚1199号</t>
-  </si>
-  <si>
-    <t>融诚1200号</t>
-  </si>
-  <si>
-    <t>融诚1201号</t>
+    <t>RC-1199</t>
+  </si>
+  <si>
+    <t>RC-1200</t>
+  </si>
+  <si>
+    <t>RC-1201</t>
   </si>
   <si>
     <t>杭州临平交通集团有限公司</t>
   </si>
   <si>
-    <t>融诚1202号</t>
+    <t>RC-1202</t>
   </si>
   <si>
     <t>湖北省联合发展投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1206号</t>
-  </si>
-  <si>
-    <t>融诚1207号</t>
+    <t>RC-1206</t>
+  </si>
+  <si>
+    <t>RC-1207</t>
   </si>
   <si>
     <t>海宁市中崛科技产业发展有限公司</t>
@@ -1223,7 +1220,7 @@
     <t>浙江兴海控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1208号</t>
+    <t>RC-1208</t>
   </si>
   <si>
     <t>浙江安吉产业控股集团有限公司</t>
@@ -1232,10 +1229,10 @@
     <t>浙江安吉两山国有控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1212号</t>
-  </si>
-  <si>
-    <t>融诚1215号</t>
+    <t>RC-1212</t>
+  </si>
+  <si>
+    <t>RC-1215</t>
   </si>
   <si>
     <t>龙港市新城建设发展集团有限公司</t>
@@ -1244,31 +1241,31 @@
     <t>龙港市国有资本运营集团有限公司</t>
   </si>
   <si>
-    <t>融诚1216号</t>
-  </si>
-  <si>
-    <t>融诚1217号</t>
-  </si>
-  <si>
-    <t>融诚1220号</t>
+    <t>RC-1216</t>
+  </si>
+  <si>
+    <t>RC-1217</t>
+  </si>
+  <si>
+    <t>RC-1220</t>
   </si>
   <si>
     <t>成都空港城市发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1223号</t>
+    <t>RC-1223</t>
   </si>
   <si>
     <t>长沙开福城投集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚1224号</t>
+    <t>RC-1224</t>
   </si>
   <si>
     <t>嘉善县国有资产投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1225号</t>
+    <t>RC-1225</t>
   </si>
   <si>
     <t>湖州申太建设发展有限公司</t>
@@ -1277,64 +1274,64 @@
     <t>湖州吴兴人才产业投资发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1227号</t>
-  </si>
-  <si>
-    <t>融诚1230号</t>
+    <t>RC-1227</t>
+  </si>
+  <si>
+    <t>RC-1230</t>
   </si>
   <si>
     <t>盐城东方投资开发集团有限公司</t>
   </si>
   <si>
-    <t>融诚1233号</t>
+    <t>RC-1233</t>
   </si>
   <si>
     <t>绍兴市镜湖开发集团有限公司</t>
   </si>
   <si>
-    <t>融诚1237号</t>
-  </si>
-  <si>
-    <t>融诚1238号</t>
-  </si>
-  <si>
-    <t>融诚1253号</t>
+    <t>RC-1237</t>
+  </si>
+  <si>
+    <t>RC-1238</t>
+  </si>
+  <si>
+    <t>RC-1253</t>
   </si>
   <si>
     <t>济南先行投资集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚1258号--第1期</t>
+    <t>RC-1258-1</t>
   </si>
   <si>
     <t>青岛西海岸新区融合控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1258号--第2期</t>
-  </si>
-  <si>
-    <t>融诚1260号</t>
+    <t>RC-1258-2</t>
+  </si>
+  <si>
+    <t>RC-1260</t>
   </si>
   <si>
     <t>常州公用产业发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1270号</t>
+    <t>RC-1270</t>
   </si>
   <si>
     <t>武汉高科国有控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1271号</t>
-  </si>
-  <si>
-    <t>融诚1277号</t>
+    <t>RC-1271</t>
+  </si>
+  <si>
+    <t>RC-1277</t>
   </si>
   <si>
     <t>淮安市城市发展投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1279号</t>
+    <t>RC-1279</t>
   </si>
   <si>
     <t>武汉临空港经济技术开发区城市建设发展投资集团有限公司</t>
@@ -1343,13 +1340,13 @@
     <t>武汉临空港国有资本控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1280号</t>
+    <t>RC-1280</t>
   </si>
   <si>
     <t>泰州市金融控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1281号</t>
+    <t>RC-1281</t>
   </si>
   <si>
     <t>无锡锡山资产经营管理有限公司</t>
@@ -1358,7 +1355,7 @@
     <t>无锡市锡州产城控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1286号</t>
+    <t>RC-1286</t>
   </si>
   <si>
     <t>青岛青发控股集团有限公司</t>
@@ -1367,7 +1364,7 @@
     <t>青岛海发国有资本投资运营集团有限公司</t>
   </si>
   <si>
-    <t>融诚1289号</t>
+    <t>RC-1289</t>
   </si>
   <si>
     <t>无锡市高新区文商旅产业集团有限公司</t>
@@ -1376,49 +1373,49 @@
     <t>无锡市吴越文旅集团有限公司</t>
   </si>
   <si>
-    <t>融诚1293号</t>
-  </si>
-  <si>
-    <t>融诚1297号</t>
-  </si>
-  <si>
-    <t>融诚1298号</t>
+    <t>RC-1293</t>
+  </si>
+  <si>
+    <t>RC-1297</t>
+  </si>
+  <si>
+    <t>RC-1298</t>
   </si>
   <si>
     <t>江苏海晟控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1299号</t>
+    <t>RC-1299</t>
   </si>
   <si>
     <t>东港投资发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1300号</t>
+    <t>RC-1300</t>
   </si>
   <si>
     <t>甘肃省公路航空旅游投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1306号</t>
+    <t>RC-1306</t>
   </si>
   <si>
     <t>泰州市交通产业集团有限公司</t>
   </si>
   <si>
-    <t>融诚1314号</t>
+    <t>RC-1314</t>
   </si>
   <si>
     <t>江苏华靖资产经营有限公司</t>
   </si>
   <si>
-    <t>融诚1315号</t>
-  </si>
-  <si>
-    <t>融诚1319号</t>
-  </si>
-  <si>
-    <t>融诚1322号</t>
+    <t>RC-1315</t>
+  </si>
+  <si>
+    <t>RC-1319</t>
+  </si>
+  <si>
+    <t>RC-1322</t>
   </si>
   <si>
     <t>成都西盛投资集团有限公司</t>
@@ -1427,28 +1424,28 @@
     <t>成都菁弘投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1328号</t>
-  </si>
-  <si>
-    <t>融诚1330号</t>
+    <t>RC-1328</t>
+  </si>
+  <si>
+    <t>RC-1330</t>
   </si>
   <si>
     <t>启东市新城建设投资发展有限公司</t>
   </si>
   <si>
-    <t>融诚1331号</t>
+    <t>RC-1331</t>
   </si>
   <si>
     <t>绍兴市上虞城市建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚1335号</t>
+    <t>RC-1335</t>
   </si>
   <si>
     <t>青岛城市建设投资(集团)有限责任公司</t>
   </si>
   <si>
-    <t>融诚1337号</t>
+    <t>RC-1337</t>
   </si>
   <si>
     <t>台州市黄岩经济开发集团有限公司</t>
@@ -1457,49 +1454,49 @@
     <t>台州市黄岩国有资本投资运营集团有限公司</t>
   </si>
   <si>
-    <t>融诚1339号</t>
+    <t>RC-1339</t>
   </si>
   <si>
     <t>中国葛洲坝集团股份有限公司</t>
   </si>
   <si>
-    <t>融诚1347-1号</t>
+    <t>RC-1347-1</t>
   </si>
   <si>
     <t>福建省晋江市建设投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1351号</t>
+    <t>RC-1351</t>
   </si>
   <si>
     <t>宁波市镇投控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1353号</t>
+    <t>RC-1353</t>
   </si>
   <si>
     <t>宁波市奉化区城市开发建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚1354号</t>
+    <t>RC-1354</t>
   </si>
   <si>
     <t>成都武侯资本投资管理集团有限公司</t>
   </si>
   <si>
-    <t>融诚1355号</t>
+    <t>RC-1355</t>
   </si>
   <si>
     <t>成都武侯产业发展投资管理集团有限公司</t>
   </si>
   <si>
-    <t>融诚1358号</t>
+    <t>RC-1358</t>
   </si>
   <si>
     <t>青岛经济技术开发区投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1365-1号</t>
+    <t>RC-1365-1</t>
   </si>
   <si>
     <t>宁海县城投集团有限公司</t>
@@ -1508,16 +1505,16 @@
     <t>宁海县启诚实业有限公司</t>
   </si>
   <si>
-    <t>融诚1365-2号</t>
-  </si>
-  <si>
-    <t>融诚1366号</t>
+    <t>RC-1365-2</t>
+  </si>
+  <si>
+    <t>RC-1366</t>
   </si>
   <si>
     <t>宁波市奉化区投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚1371号</t>
+    <t>RC-1371</t>
   </si>
   <si>
     <t>无锡欣致科技产业有限公司</t>
@@ -1526,34 +1523,34 @@
     <t>无锡市锡山城市建设发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1376号</t>
+    <t>RC-1376</t>
   </si>
   <si>
     <t>宁波南创控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1378号</t>
-  </si>
-  <si>
-    <t>融诚1379号</t>
+    <t>RC-1378</t>
+  </si>
+  <si>
+    <t>RC-1379</t>
   </si>
   <si>
     <t>徐州市产业发展控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1382号</t>
-  </si>
-  <si>
-    <t>融诚1385号</t>
+    <t>RC-1382</t>
+  </si>
+  <si>
+    <t>RC-1385</t>
   </si>
   <si>
     <t>徐州高新控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1393号</t>
-  </si>
-  <si>
-    <t>融诚1396号</t>
+    <t>RC-1393</t>
+  </si>
+  <si>
+    <t>RC-1396</t>
   </si>
   <si>
     <t>江苏云港发展集团有限公司</t>
@@ -1562,91 +1559,91 @@
     <t>江苏海州湾控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚1398号</t>
+    <t>RC-1398</t>
   </si>
   <si>
     <t>江苏海润城市发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚1399号</t>
+    <t>RC-1399</t>
   </si>
   <si>
     <t>蚌埠中城国有资本投资运营有限公司</t>
   </si>
   <si>
-    <t>融诚1400号</t>
-  </si>
-  <si>
-    <t>融诚1404号</t>
+    <t>RC-1400</t>
+  </si>
+  <si>
+    <t>RC-1404</t>
   </si>
   <si>
     <t>烟台市福山区国有控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚728号</t>
+    <t>RC-728</t>
   </si>
   <si>
     <t>青岛金家岭控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚822号</t>
+    <t>RC-822</t>
   </si>
   <si>
     <t>青岛西海岸新区海洋控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚837号</t>
-  </si>
-  <si>
-    <t>融诚846号</t>
-  </si>
-  <si>
-    <t>融诚848号</t>
+    <t>RC-837</t>
+  </si>
+  <si>
+    <t>RC-846</t>
+  </si>
+  <si>
+    <t>RC-848</t>
   </si>
   <si>
     <t>泉州城建集团有限公司</t>
   </si>
   <si>
-    <t>融诚866号</t>
+    <t>RC-866</t>
   </si>
   <si>
     <t>福州城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚868号</t>
+    <t>RC-868</t>
   </si>
   <si>
     <t>杭州萧山交通投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚880号</t>
+    <t>RC-880</t>
   </si>
   <si>
     <t>宁波城建投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚906号</t>
-  </si>
-  <si>
-    <t>融诚908号</t>
-  </si>
-  <si>
-    <t>融诚916号</t>
+    <t>RC-906</t>
+  </si>
+  <si>
+    <t>RC-908</t>
+  </si>
+  <si>
+    <t>RC-916</t>
   </si>
   <si>
     <t>宜宾三江投资建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚946号</t>
-  </si>
-  <si>
-    <t>融诚948号</t>
-  </si>
-  <si>
-    <t>融诚955号</t>
-  </si>
-  <si>
-    <t>融诚957号</t>
+    <t>RC-946</t>
+  </si>
+  <si>
+    <t>RC-948</t>
+  </si>
+  <si>
+    <t>RC-955</t>
+  </si>
+  <si>
+    <t>RC-957</t>
   </si>
   <si>
     <t>长沙天心城市发展集团有限公司</t>
@@ -1655,34 +1652,34 @@
     <t>长沙天心城市建设投资开发集团有限公司</t>
   </si>
   <si>
-    <t>融诚959号</t>
+    <t>RC-959</t>
   </si>
   <si>
     <t>石家庄国控城市发展投资集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚966号</t>
+    <t>RC-966</t>
   </si>
   <si>
     <t>南通国有资产投资控股有限公司</t>
   </si>
   <si>
-    <t>融诚983号</t>
+    <t>RC-983</t>
   </si>
   <si>
     <t>岳阳市城市建设投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚985号</t>
+    <t>RC-985</t>
   </si>
   <si>
     <t>伊犁哈萨克自治州财通国有资产经营有限责任公司</t>
   </si>
   <si>
-    <t>融诚994号</t>
-  </si>
-  <si>
-    <t>融诚博盈40006号</t>
+    <t>RC-994</t>
+  </si>
+  <si>
+    <t>RCBY-40006</t>
   </si>
   <si>
     <t>肇庆市高晟城市投资发展集团有限公司</t>
@@ -1691,76 +1688,76 @@
     <t>肇庆市高要建投投资开发集团有限公司</t>
   </si>
   <si>
-    <t>融诚博盈40007号</t>
+    <t>RCBY-40007</t>
   </si>
   <si>
     <t>宜宾发展控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚博盈40009号</t>
+    <t>RCBY-40009</t>
   </si>
   <si>
     <t>马鞍山市国有资本投资运营控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚博盈40011号</t>
+    <t>RCBY-40011</t>
   </si>
   <si>
     <t>知识城（广州）投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚博盈40013号</t>
-  </si>
-  <si>
-    <t>融诚丰享16号</t>
+    <t>RCBY-40013</t>
+  </si>
+  <si>
+    <t>RCFX-16</t>
   </si>
   <si>
     <t>安徽西湖投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰享1号</t>
-  </si>
-  <si>
-    <t>融诚丰享30号</t>
+    <t>RCFX-1</t>
+  </si>
+  <si>
+    <t>RCFX-30</t>
   </si>
   <si>
     <t>西部（重庆）科学城江津园区开发建设集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰享75号</t>
+    <t>RCFX-75</t>
   </si>
   <si>
     <t>泰州市泰政交通投资有限公司</t>
   </si>
   <si>
-    <t>融诚丰享88号</t>
-  </si>
-  <si>
-    <t>融诚丰享89号</t>
+    <t>RCFX-88</t>
+  </si>
+  <si>
+    <t>RCFX-89</t>
   </si>
   <si>
     <t>无锡市梁溪产业发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰享90号</t>
+    <t>RCFX-90</t>
   </si>
   <si>
     <t>扬州江淮建设发展有限公司</t>
   </si>
   <si>
-    <t>融诚丰享92号</t>
+    <t>RCFX-92</t>
   </si>
   <si>
     <t>成都经开资产管理有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0001号</t>
+    <t>RCFY-H-0001</t>
   </si>
   <si>
     <t>浙江省德清县交通水利投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0002号</t>
+    <t>RCFY-H-0002</t>
   </si>
   <si>
     <t>浙江安吉修竹绿化工程有限公司</t>
@@ -1769,13 +1766,13 @@
     <t>浙江安吉国控建设发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0003号</t>
+    <t>RCFY-H-0003</t>
   </si>
   <si>
     <t>安吉县产业投资发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0004号</t>
+    <t>RCFY-H-0004</t>
   </si>
   <si>
     <t>湖州莫干山高新产业投资发展集团有限公司</t>
@@ -1784,13 +1781,13 @@
     <t>湖州莫干山国有资本控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0006号</t>
+    <t>RCFY-H-0006</t>
   </si>
   <si>
     <t>湖州莫干山高新集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0008号</t>
+    <t>RCFY-H-0008</t>
   </si>
   <si>
     <t>平阳县城市建设投资有限公司</t>
@@ -1799,13 +1796,13 @@
     <t>平阳县国资发展有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0009号</t>
+    <t>RCFY-H-0009</t>
   </si>
   <si>
     <t>浙江南太湖控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0011号</t>
+    <t>RCFY-H-0011</t>
   </si>
   <si>
     <t>浙江天子湖实业投资有限公司</t>
@@ -1814,13 +1811,13 @@
     <t>浙江安吉建设控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0013号</t>
+    <t>RCFY-H-0013</t>
   </si>
   <si>
     <t>湖州市城市投资发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈H-0015号</t>
+    <t>RCFY-H-0015</t>
   </si>
   <si>
     <t>湖州吴兴国有资本投资发展有限公司</t>
@@ -1829,7 +1826,7 @@
     <t>湖州吴兴交通旅游投资发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-001号</t>
+    <t>RCFY-Z-001</t>
   </si>
   <si>
     <t>江苏金坛建设集团有限公司</t>
@@ -1838,37 +1835,37 @@
     <t>江苏长荡湖旅游控股有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-002号</t>
+    <t>RCFY-Z-002</t>
   </si>
   <si>
     <t>江苏金坛投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-003号</t>
+    <t>RCFY-Z-003</t>
   </si>
   <si>
     <t>江苏金坛滨湖新城开发建设有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-004号</t>
+    <t>RCFY-Z-004</t>
   </si>
   <si>
     <t>常州市茅山投资控股有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-005号</t>
+    <t>RCFY-Z-005</t>
   </si>
   <si>
     <t>江苏伟驰控股发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-006号</t>
+    <t>RCFY-Z-006</t>
   </si>
   <si>
     <t>常州嘉发控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-008号</t>
+    <t>RCFY-Z-008</t>
   </si>
   <si>
     <t>平湖市独山港经济开发区投资集团有限公司</t>
@@ -1877,10 +1874,10 @@
     <t>平湖市城市发展投资（集团）有限公司</t>
   </si>
   <si>
-    <t>融诚丰盈Z-009号</t>
-  </si>
-  <si>
-    <t>融诚恒鑫1号</t>
+    <t>RCFY-Z-009</t>
+  </si>
+  <si>
+    <t>RCHX-1</t>
   </si>
   <si>
     <t>长兴城市建设投资集团有限公司</t>
@@ -1889,103 +1886,103 @@
     <t>浙江长兴创新投资集团有限公司</t>
   </si>
   <si>
-    <t>融诚天盈10号</t>
-  </si>
-  <si>
-    <t>融诚天盈1号</t>
+    <t>RCTY-10</t>
+  </si>
+  <si>
+    <t>RCTY-1</t>
   </si>
   <si>
     <t>绍兴市上虞杭州湾经开区控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚天盈2号</t>
+    <t>RCTY-2</t>
   </si>
   <si>
     <t>绍兴滨海新区发展集团有限公司</t>
   </si>
   <si>
-    <t>融诚天盈3号</t>
-  </si>
-  <si>
-    <t>融诚天盈5号</t>
-  </si>
-  <si>
-    <t>融诚天盈7号</t>
-  </si>
-  <si>
-    <t>融诚天盈8号</t>
+    <t>RCTY-3</t>
+  </si>
+  <si>
+    <t>RCTY-5</t>
+  </si>
+  <si>
+    <t>RCTY-7</t>
+  </si>
+  <si>
+    <t>RCTY-8</t>
   </si>
   <si>
     <t>宿迁国开投资控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚天盈9号</t>
+    <t>RCTY-9</t>
   </si>
   <si>
     <t>赣州城市投资控股集团有限责任公司</t>
   </si>
   <si>
-    <t>融诚永盈3号</t>
+    <t>RCYY-3</t>
   </si>
   <si>
     <t>内蒙古兴业银锡矿业股份有限公司</t>
   </si>
   <si>
-    <t>融诚永盈7号</t>
-  </si>
-  <si>
-    <t>融诚永盈8号</t>
+    <t>RCYY-7</t>
+  </si>
+  <si>
+    <t>RCYY-8</t>
   </si>
   <si>
     <t>吉安城投控股集团有限公司</t>
   </si>
   <si>
-    <t>瑞盈固收1号</t>
+    <t>RYGS-1</t>
   </si>
   <si>
     <t>江苏瑞海投资控股集团有限公司</t>
   </si>
   <si>
-    <t>瑞盈固收2号</t>
+    <t>RYGS-2</t>
   </si>
   <si>
     <t>常州溪城现代农业发展有限公司</t>
   </si>
   <si>
-    <t>瑞盈固收5号</t>
+    <t>RYGS-5</t>
   </si>
   <si>
     <t>成都市郫都区城乡投资建设开发有限公司</t>
   </si>
   <si>
-    <t>稳健102号单一资金信托</t>
+    <t>WJ-102</t>
   </si>
   <si>
     <t>高峰（迁安）糖业有限公司</t>
   </si>
   <si>
-    <t>稳健2212号单一资金信托</t>
+    <t>WJ-2212</t>
   </si>
   <si>
     <t>湘潭市城市建设投资经营有限责任公司</t>
   </si>
   <si>
-    <t>稳盈317号</t>
+    <t>WY-317</t>
   </si>
   <si>
     <t>重庆远腾房地产开发有限公司</t>
   </si>
   <si>
-    <t>稳盈601号</t>
-  </si>
-  <si>
-    <t>稳盈731号</t>
+    <t>WY-601</t>
+  </si>
+  <si>
+    <t>WY-731</t>
   </si>
   <si>
     <t>成都高投产城建设集团有限公司</t>
   </si>
   <si>
-    <t>颐养1号养老产业</t>
+    <t>YY-1</t>
   </si>
   <si>
     <t>中金投资（集团）有限公司</t>
@@ -1994,7 +1991,7 @@
     <t>周传有,胡杨</t>
   </si>
   <si>
-    <t>融诚天盈11号</t>
+    <t>RCTY-11</t>
   </si>
   <si>
     <t>乌镇实业(桐乡)有限公司</t>
@@ -2003,10 +2000,10 @@
     <t>桐乡市国有资本控股集团有限公司</t>
   </si>
   <si>
-    <t>融诚天盈12号</t>
-  </si>
-  <si>
-    <t>融诚天盈16号</t>
+    <t>RCTY-12</t>
+  </si>
+  <si>
+    <t>RCTY-16</t>
   </si>
   <si>
     <t>桐乡市工业发展投资集团有限公司</t>
@@ -2028,12 +2025,11 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2041,7 +2037,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2049,14 +2045,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2064,7 +2060,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2072,7 +2068,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2080,7 +2076,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2088,7 +2084,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2096,14 +2092,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2111,7 +2107,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2119,7 +2115,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2127,14 +2123,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2142,42 +2138,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -2630,12 +2626,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2690,7 +2689,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2700,7 +2913,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2742,74 +2955,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2817,51 +2970,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -2870,13 +2987,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2910,24 +3027,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2953,7 +3059,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -2975,56 +3081,17 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet2"/>
+  <sheetPr/>
   <dimension ref="A1:C358"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="31.8" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="35.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="35.75" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
@@ -3042,29 +3109,23 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -3075,29 +3136,23 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -3108,29 +3163,23 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -3141,7 +3190,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -3152,7 +3201,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -3163,139 +3212,103 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -3306,18 +3319,15 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -3328,7 +3338,7 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -3339,7 +3349,7 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -3350,7 +3360,7 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -3361,7 +3371,7 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -3372,7 +3382,7 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -3383,18 +3393,15 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -3405,7 +3412,7 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -3416,7 +3423,7 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -3427,29 +3434,23 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -3460,7 +3461,7 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -3471,7 +3472,7 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -3482,7 +3483,7 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -3493,7 +3494,7 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -3504,18 +3505,15 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -3526,7 +3524,7 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -3537,7 +3535,7 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -3548,18 +3546,15 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -3570,7 +3565,7 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -3581,29 +3576,23 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="3" t="s">
         <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -3614,7 +3603,7 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -3625,7 +3614,7 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -3636,7 +3625,7 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -3647,29 +3636,23 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="3" t="s">
         <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -3680,7 +3663,7 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -3691,7 +3674,7 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -3702,7 +3685,7 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="3" t="s">
         <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -3713,7 +3696,7 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -3724,7 +3707,7 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -3735,18 +3718,15 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="3" t="s">
         <v>134</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -3757,139 +3737,103 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="3" t="s">
         <v>137</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C71" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="3" t="s">
         <v>138</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C73" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C74" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C75" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="3" t="s">
         <v>143</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C76" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C77" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C78" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -3900,7 +3844,7 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -3911,7 +3855,7 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -3922,7 +3866,7 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -3933,7 +3877,7 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -3944,7 +3888,7 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -3955,7 +3899,7 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -3966,7 +3910,7 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -3977,172 +3921,127 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C87" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="3" t="s">
         <v>155</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C88" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C89" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="3" t="s">
         <v>159</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C90" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="3" t="s">
         <v>161</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C91" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C92" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="3" t="s">
         <v>164</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="3" t="s">
         <v>165</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C94" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C95" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C96" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="3" t="s">
         <v>171</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C97" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="3" t="s">
         <v>173</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C98" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="3" t="s">
         <v>174</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C99" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="3" t="s">
         <v>176</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C100" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="3" t="s">
         <v>178</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C101" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -4153,51 +4052,39 @@
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="3" t="s">
         <v>183</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C103" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C104" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C105" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C106" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="3" t="s">
         <v>190</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -4208,18 +4095,15 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C108" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="3" t="s">
         <v>194</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -4230,40 +4114,31 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C110" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C111" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C112" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="3" t="s">
         <v>203</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -4274,161 +4149,119 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="3" t="s">
         <v>206</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C114" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="3" t="s">
         <v>208</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C115" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C116" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="3" t="s">
         <v>211</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C117" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C118" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="3" t="s">
         <v>214</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C119" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C120" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C121" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="3" t="s">
         <v>220</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C122" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="3" t="s">
         <v>221</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C123" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="3" t="s">
         <v>223</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C124" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="3" t="s">
         <v>225</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C125" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="3" t="s">
         <v>227</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C126" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="3" t="s">
         <v>229</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C127" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="3" t="s">
         <v>231</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -4438,723 +4271,528 @@
         <v>233</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="1" t="s">
+    <row r="129" spans="1:2">
+      <c r="A129" s="3" t="s">
         <v>234</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C129" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="1" t="s">
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="3" t="s">
         <v>236</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C130" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="1" t="s">
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="3" t="s">
         <v>238</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C131" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="1" t="s">
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="3" t="s">
         <v>240</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C132" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="1" t="s">
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="3" t="s">
         <v>242</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C133" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="1" t="s">
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="3" t="s">
         <v>244</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C134" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" s="1" t="s">
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="3" t="s">
         <v>246</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C135" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" s="1" t="s">
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="3" t="s">
         <v>248</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C136" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" s="1" t="s">
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="3" t="s">
         <v>250</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C137" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="1" t="s">
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="3" t="s">
         <v>252</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C138" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" s="1" t="s">
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="3" t="s">
         <v>254</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C139" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" s="1" t="s">
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="3" t="s">
         <v>256</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C140" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" s="1" t="s">
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="3" t="s">
         <v>258</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C141" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" s="1" t="s">
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="3" t="s">
         <v>260</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C142" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="1" t="s">
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="3" t="s">
         <v>262</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C143" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="1" t="s">
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="3" t="s">
         <v>264</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C144" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="1" t="s">
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C145" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" s="1" t="s">
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C146" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" s="1" t="s">
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="3" t="s">
         <v>269</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C147" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" s="1" t="s">
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="3" t="s">
         <v>271</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C148" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" s="1" t="s">
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="3" t="s">
         <v>272</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C149" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" s="1" t="s">
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="3" t="s">
         <v>274</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C150" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" s="1" t="s">
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="3" t="s">
         <v>276</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C151" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" s="1" t="s">
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="3" t="s">
         <v>278</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C152" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" s="1" t="s">
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="3" t="s">
         <v>280</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C153" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="1" t="s">
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="3" t="s">
         <v>282</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C154" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" s="1" t="s">
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="3" t="s">
         <v>284</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C155" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" s="1" t="s">
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="3" t="s">
         <v>285</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C156" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" s="1" t="s">
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="3" t="s">
         <v>287</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C157" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" s="1" t="s">
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="3" t="s">
         <v>289</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C158" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="1" t="s">
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="3" t="s">
         <v>291</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C159" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="1" t="s">
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="3" t="s">
         <v>293</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C160" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" s="1" t="s">
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="3" t="s">
         <v>295</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C161" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="1" t="s">
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="3" t="s">
         <v>296</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C162" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="1" t="s">
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="3" t="s">
         <v>298</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C163" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1" t="s">
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="3" t="s">
         <v>300</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C164" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="1" t="s">
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="3" t="s">
         <v>302</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C165" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="1" t="s">
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="3" t="s">
         <v>304</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C166" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="1" t="s">
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="3" t="s">
         <v>306</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C167" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="1" t="s">
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="3" t="s">
         <v>308</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C168" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="1" t="s">
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="3" t="s">
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C169" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="1" t="s">
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="3" t="s">
         <v>311</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C170" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="1" t="s">
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="3" t="s">
         <v>312</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C171" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="1" t="s">
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="3" t="s">
         <v>314</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C172" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" s="1" t="s">
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="3" t="s">
         <v>316</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C173" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" s="1" t="s">
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="3" t="s">
         <v>317</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C174" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="1" t="s">
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="3" t="s">
         <v>319</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C175" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" s="1" t="s">
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="3" t="s">
         <v>321</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C176" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="1" t="s">
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="3" t="s">
         <v>323</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C177" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="1" t="s">
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="3" t="s">
         <v>325</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C178" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="1" t="s">
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="3" t="s">
         <v>326</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C179" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="1" t="s">
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="3" t="s">
         <v>328</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C180" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" s="1" t="s">
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C181" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="1" t="s">
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="3" t="s">
         <v>332</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C182" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" s="1" t="s">
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="3" t="s">
         <v>333</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C183" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="1" t="s">
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="3" t="s">
         <v>335</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C184" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" s="1" t="s">
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="3" t="s">
         <v>337</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C185" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="1" t="s">
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="3" t="s">
         <v>338</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C186" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="1" t="s">
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="3" t="s">
         <v>339</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C187" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" s="1" t="s">
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="3" t="s">
         <v>340</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C188" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="1" t="s">
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="3" t="s">
         <v>342</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C189" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="1" t="s">
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="3" t="s">
         <v>343</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C190" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="1" t="s">
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="3" t="s">
         <v>344</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C191" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="1" t="s">
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="3" t="s">
         <v>345</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C192" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="3" t="s">
         <v>347</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C193" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="1" t="s">
+      <c r="A194" s="3" t="s">
         <v>349</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -5165,62 +4803,47 @@
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="1" t="s">
+      <c r="A195" s="3" t="s">
         <v>352</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C195" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196" s="1" t="s">
+      <c r="A196" s="3" t="s">
         <v>354</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C196" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="1" t="s">
+      <c r="A197" s="3" t="s">
         <v>355</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C197" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="1" t="s">
+      <c r="A198" s="3" t="s">
         <v>357</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C198" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="1" t="s">
+      <c r="A199" s="3" t="s">
         <v>358</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C199" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="1" t="s">
+      <c r="A200" s="3" t="s">
         <v>359</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -5231,18 +4854,15 @@
       </c>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="1" t="s">
+      <c r="A201" s="3" t="s">
         <v>360</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C201" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="1" t="s">
+      <c r="A202" s="3" t="s">
         <v>362</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -5253,194 +4873,143 @@
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="1" t="s">
+      <c r="A203" s="3" t="s">
         <v>365</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C203" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204" s="1" t="s">
+      <c r="A204" s="3" t="s">
         <v>367</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C204" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="1" t="s">
+      <c r="A205" s="3" t="s">
         <v>368</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C205" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="1" t="s">
+      <c r="A206" s="3" t="s">
         <v>369</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C206" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="1" t="s">
+      <c r="A207" s="3" t="s">
         <v>371</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C207" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="1" t="s">
+      <c r="A208" s="3" t="s">
         <v>373</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C208" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="1" t="s">
+      <c r="A209" s="3" t="s">
         <v>375</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C209" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="1" t="s">
+      <c r="A210" s="3" t="s">
         <v>377</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C210" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="1" t="s">
+      <c r="A211" s="3" t="s">
         <v>379</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C211" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="1" t="s">
+      <c r="A212" s="3" t="s">
         <v>381</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C212" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="1" t="s">
+      <c r="A213" s="3" t="s">
         <v>383</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C213" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="1" t="s">
+      <c r="A214" s="3" t="s">
         <v>385</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C214" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="1" t="s">
+      <c r="A215" s="3" t="s">
         <v>387</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C215" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="1" t="s">
+      <c r="A216" s="3" t="s">
         <v>388</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C216" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="1" t="s">
+      <c r="A217" s="3" t="s">
         <v>389</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C217" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="3" t="s">
         <v>391</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C218" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="1" t="s">
+      <c r="A219" s="3" t="s">
         <v>393</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C219" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="1" t="s">
+      <c r="A220" s="3" t="s">
         <v>394</v>
       </c>
       <c r="B220" s="2" t="s">
@@ -5451,7 +5020,7 @@
       </c>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="1" t="s">
+      <c r="A221" s="3" t="s">
         <v>397</v>
       </c>
       <c r="B221" s="2" t="s">
@@ -5462,18 +5031,15 @@
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="1" t="s">
+      <c r="A222" s="3" t="s">
         <v>400</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C222" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="1" t="s">
+      <c r="A223" s="3" t="s">
         <v>401</v>
       </c>
       <c r="B223" s="2" t="s">
@@ -5484,7 +5050,7 @@
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="1" t="s">
+      <c r="A224" s="3" t="s">
         <v>404</v>
       </c>
       <c r="B224" s="2" t="s">
@@ -5495,18 +5061,15 @@
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225" s="1" t="s">
+      <c r="A225" s="3" t="s">
         <v>405</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C225" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="1" t="s">
+      <c r="A226" s="3" t="s">
         <v>406</v>
       </c>
       <c r="B226" s="2" t="s">
@@ -5517,29 +5080,23 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="1" t="s">
+      <c r="A227" s="3" t="s">
         <v>408</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C227" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="1" t="s">
+      <c r="A228" s="3" t="s">
         <v>410</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C228" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="1" t="s">
+      <c r="A229" s="3" t="s">
         <v>412</v>
       </c>
       <c r="B229" s="2" t="s">
@@ -5550,7 +5107,7 @@
       </c>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="1" t="s">
+      <c r="A230" s="3" t="s">
         <v>415</v>
       </c>
       <c r="B230" s="2" t="s">
@@ -5561,40 +5118,31 @@
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="1" t="s">
+      <c r="A231" s="3" t="s">
         <v>416</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C231" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="232" spans="1:3">
-      <c r="A232" s="1" t="s">
+      <c r="A232" s="3" t="s">
         <v>418</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C232" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="3" t="s">
         <v>420</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C233" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="1" t="s">
+      <c r="A234" s="3" t="s">
         <v>421</v>
       </c>
       <c r="B234" s="2" t="s">
@@ -5605,84 +5153,63 @@
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="1" t="s">
+      <c r="A235" s="3" t="s">
         <v>422</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C235" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="1" t="s">
+      <c r="A236" s="3" t="s">
         <v>424</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C236" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="1" t="s">
+      <c r="A237" s="3" t="s">
         <v>426</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C237" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="1" t="s">
+      <c r="A238" s="3" t="s">
         <v>427</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C238" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239" s="1" t="s">
+      <c r="A239" s="3" t="s">
         <v>429</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C239" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="240" spans="1:3">
-      <c r="A240" s="1" t="s">
+      <c r="A240" s="3" t="s">
         <v>431</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C240" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="241" spans="1:3">
-      <c r="A241" s="1" t="s">
+      <c r="A241" s="3" t="s">
         <v>432</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C241" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="1" t="s">
+      <c r="A242" s="3" t="s">
         <v>434</v>
       </c>
       <c r="B242" s="2" t="s">
@@ -5693,7 +5220,7 @@
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="1" t="s">
+      <c r="A243" s="3" t="s">
         <v>437</v>
       </c>
       <c r="B243" s="2" t="s">
@@ -5704,7 +5231,7 @@
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="1" t="s">
+      <c r="A244" s="3" t="s">
         <v>439</v>
       </c>
       <c r="B244" s="2" t="s">
@@ -5715,7 +5242,7 @@
       </c>
     </row>
     <row r="245" spans="1:3">
-      <c r="A245" s="1" t="s">
+      <c r="A245" s="3" t="s">
         <v>442</v>
       </c>
       <c r="B245" s="2" t="s">
@@ -5726,7 +5253,7 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="1" t="s">
+      <c r="A246" s="3" t="s">
         <v>445</v>
       </c>
       <c r="B246" s="2" t="s">
@@ -5737,106 +5264,79 @@
       </c>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="1" t="s">
+      <c r="A247" s="3" t="s">
         <v>448</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C247" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248" s="1" t="s">
+      <c r="A248" s="3" t="s">
         <v>449</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C248" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="1" t="s">
+      <c r="A249" s="3" t="s">
         <v>450</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C249" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250" s="1" t="s">
+      <c r="A250" s="3" t="s">
         <v>452</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="C250" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="1" t="s">
+      <c r="A251" s="3" t="s">
         <v>454</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C251" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="1" t="s">
+      <c r="A252" s="3" t="s">
         <v>456</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C252" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="1" t="s">
+      <c r="A253" s="3" t="s">
         <v>458</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C253" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="1" t="s">
+      <c r="A254" s="3" t="s">
         <v>460</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C254" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="1" t="s">
+      <c r="A255" s="3" t="s">
         <v>461</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C255" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="256" spans="1:3">
-      <c r="A256" s="1" t="s">
+      <c r="A256" s="3" t="s">
         <v>462</v>
       </c>
       <c r="B256" s="2" t="s">
@@ -5847,51 +5347,39 @@
       </c>
     </row>
     <row r="257" spans="1:3">
-      <c r="A257" s="1" t="s">
+      <c r="A257" s="3" t="s">
         <v>465</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C257" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="258" spans="1:3">
-      <c r="A258" s="1" t="s">
+      <c r="A258" s="3" t="s">
         <v>466</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C258" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="1" t="s">
+      <c r="A259" s="3" t="s">
         <v>468</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C259" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="1" t="s">
+      <c r="A260" s="3" t="s">
         <v>470</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C260" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261" s="1" t="s">
+      <c r="A261" s="3" t="s">
         <v>472</v>
       </c>
       <c r="B261" s="2" t="s">
@@ -5902,84 +5390,63 @@
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="1" t="s">
+      <c r="A262" s="3" t="s">
         <v>475</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C262" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="1" t="s">
+      <c r="A263" s="3" t="s">
         <v>477</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C263" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="1" t="s">
+      <c r="A264" s="3" t="s">
         <v>479</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C264" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="1" t="s">
+      <c r="A265" s="3" t="s">
         <v>481</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C265" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266" s="1" t="s">
+      <c r="A266" s="3" t="s">
         <v>483</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C266" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="1" t="s">
+      <c r="A267" s="3" t="s">
         <v>485</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C267" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="1" t="s">
+      <c r="A268" s="3" t="s">
         <v>487</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C268" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="1" t="s">
+      <c r="A269" s="3" t="s">
         <v>489</v>
       </c>
       <c r="B269" s="2" t="s">
@@ -5990,7 +5457,7 @@
       </c>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="1" t="s">
+      <c r="A270" s="3" t="s">
         <v>492</v>
       </c>
       <c r="B270" s="2" t="s">
@@ -6001,18 +5468,15 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="1" t="s">
+      <c r="A271" s="3" t="s">
         <v>493</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C271" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="1" t="s">
+      <c r="A272" s="3" t="s">
         <v>495</v>
       </c>
       <c r="B272" s="2" t="s">
@@ -6023,62 +5487,47 @@
       </c>
     </row>
     <row r="273" spans="1:3">
-      <c r="A273" s="1" t="s">
+      <c r="A273" s="3" t="s">
         <v>498</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="C273" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="1" t="s">
+      <c r="A274" s="3" t="s">
         <v>500</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C274" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275" s="1" t="s">
+      <c r="A275" s="3" t="s">
         <v>501</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C275" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="1" t="s">
+      <c r="A276" s="3" t="s">
         <v>503</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C276" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="1" t="s">
+      <c r="A277" s="3" t="s">
         <v>504</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C277" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="1" t="s">
+      <c r="A278" s="3" t="s">
         <v>506</v>
       </c>
       <c r="B278" s="2" t="s">
@@ -6089,7 +5538,7 @@
       </c>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="1" t="s">
+      <c r="A279" s="3" t="s">
         <v>507</v>
       </c>
       <c r="B279" s="2" t="s">
@@ -6100,205 +5549,151 @@
       </c>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="1" t="s">
+      <c r="A280" s="3" t="s">
         <v>510</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="C280" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281" s="1" t="s">
+      <c r="A281" s="3" t="s">
         <v>512</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C281" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282" s="1" t="s">
+      <c r="A282" s="3" t="s">
         <v>514</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C282" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" s="1" t="s">
+      <c r="A283" s="3" t="s">
         <v>515</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C283" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="1" t="s">
+      <c r="A284" s="3" t="s">
         <v>517</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="C284" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="1" t="s">
+      <c r="A285" s="3" t="s">
         <v>519</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="C285" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="1" t="s">
+      <c r="A286" s="3" t="s">
         <v>521</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C286" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="1" t="s">
+      <c r="A287" s="3" t="s">
         <v>522</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C287" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="1" t="s">
+      <c r="A288" s="3" t="s">
         <v>523</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C288" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="289" spans="1:3">
-      <c r="A289" s="1" t="s">
+      <c r="A289" s="3" t="s">
         <v>525</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C289" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="290" spans="1:3">
-      <c r="A290" s="1" t="s">
+      <c r="A290" s="3" t="s">
         <v>527</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C290" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="291" spans="1:3">
-      <c r="A291" s="1" t="s">
+      <c r="A291" s="3" t="s">
         <v>529</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C291" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="1" t="s">
+      <c r="A292" s="3" t="s">
         <v>531</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C292" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="1" t="s">
+      <c r="A293" s="3" t="s">
         <v>532</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C293" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="294" spans="1:3">
-      <c r="A294" s="1" t="s">
+      <c r="A294" s="3" t="s">
         <v>533</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C294" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="1" t="s">
+      <c r="A295" s="3" t="s">
         <v>535</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C295" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="1" t="s">
+      <c r="A296" s="3" t="s">
         <v>536</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C296" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="297" spans="1:3">
-      <c r="A297" s="1" t="s">
+      <c r="A297" s="3" t="s">
         <v>537</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C297" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="298" spans="1:3">
-      <c r="A298" s="1" t="s">
+      <c r="A298" s="3" t="s">
         <v>538</v>
       </c>
       <c r="B298" s="2" t="s">
@@ -6309,62 +5704,47 @@
       </c>
     </row>
     <row r="299" spans="1:3">
-      <c r="A299" s="1" t="s">
+      <c r="A299" s="3" t="s">
         <v>541</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C299" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="1" t="s">
+      <c r="A300" s="3" t="s">
         <v>543</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C300" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="1" t="s">
+      <c r="A301" s="3" t="s">
         <v>545</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C301" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="302" spans="1:3">
-      <c r="A302" s="1" t="s">
+      <c r="A302" s="3" t="s">
         <v>547</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C302" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="1" t="s">
+      <c r="A303" s="3" t="s">
         <v>549</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C303" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="1" t="s">
+      <c r="A304" s="3" t="s">
         <v>550</v>
       </c>
       <c r="B304" s="2" t="s">
@@ -6375,7 +5755,7 @@
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="1" t="s">
+      <c r="A305" s="3" t="s">
         <v>553</v>
       </c>
       <c r="B305" s="2" t="s">
@@ -6386,73 +5766,55 @@
       </c>
     </row>
     <row r="306" spans="1:3">
-      <c r="A306" s="1" t="s">
+      <c r="A306" s="3" t="s">
         <v>555</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C306" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="307" spans="1:3">
-      <c r="A307" s="1" t="s">
+      <c r="A307" s="3" t="s">
         <v>557</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C307" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="1" t="s">
+      <c r="A308" s="3" t="s">
         <v>559</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C308" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="1" t="s">
+      <c r="A309" s="3" t="s">
         <v>560</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="C309" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="A310" s="1" t="s">
+      <c r="A310" s="3" t="s">
         <v>562</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C310" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="1" t="s">
+      <c r="A311" s="3" t="s">
         <v>563</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C311" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="1" t="s">
+      <c r="A312" s="3" t="s">
         <v>565</v>
       </c>
       <c r="B312" s="2" t="s">
@@ -6463,62 +5825,47 @@
       </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="A313" s="1" t="s">
+      <c r="A313" s="3" t="s">
         <v>567</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C313" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="1" t="s">
+      <c r="A314" s="3" t="s">
         <v>568</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C314" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="1" t="s">
+      <c r="A315" s="3" t="s">
         <v>570</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C315" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="3" t="s">
         <v>572</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="C316" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="1" t="s">
+      <c r="A317" s="3" t="s">
         <v>574</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C317" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="1" t="s">
+      <c r="A318" s="3" t="s">
         <v>576</v>
       </c>
       <c r="B318" s="2" t="s">
@@ -6529,7 +5876,7 @@
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="1" t="s">
+      <c r="A319" s="3" t="s">
         <v>579</v>
       </c>
       <c r="B319" s="2" t="s">
@@ -6540,7 +5887,7 @@
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="1" t="s">
+      <c r="A320" s="3" t="s">
         <v>581</v>
       </c>
       <c r="B320" s="2" t="s">
@@ -6551,18 +5898,15 @@
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="A321" s="1" t="s">
+      <c r="A321" s="3" t="s">
         <v>584</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C321" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="322" spans="1:3">
-      <c r="A322" s="1" t="s">
+      <c r="A322" s="3" t="s">
         <v>586</v>
       </c>
       <c r="B322" s="2" t="s">
@@ -6573,7 +5917,7 @@
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="1" t="s">
+      <c r="A323" s="3" t="s">
         <v>589</v>
       </c>
       <c r="B323" s="2" t="s">
@@ -6584,7 +5928,7 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="1" t="s">
+      <c r="A324" s="3" t="s">
         <v>591</v>
       </c>
       <c r="B324" s="2" t="s">
@@ -6595,18 +5939,15 @@
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="1" t="s">
+      <c r="A325" s="3" t="s">
         <v>594</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="C325" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="326" spans="1:3">
-      <c r="A326" s="1" t="s">
+      <c r="A326" s="3" t="s">
         <v>596</v>
       </c>
       <c r="B326" s="2" t="s">
@@ -6617,7 +5958,7 @@
       </c>
     </row>
     <row r="327" spans="1:3">
-      <c r="A327" s="1" t="s">
+      <c r="A327" s="3" t="s">
         <v>599</v>
       </c>
       <c r="B327" s="2" t="s">
@@ -6628,18 +5969,15 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="1" t="s">
+      <c r="A328" s="3" t="s">
         <v>602</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C328" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="1" t="s">
+      <c r="A329" s="3" t="s">
         <v>604</v>
       </c>
       <c r="B329" s="2" t="s">
@@ -6650,7 +5988,7 @@
       </c>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="1" t="s">
+      <c r="A330" s="3" t="s">
         <v>606</v>
       </c>
       <c r="B330" s="2" t="s">
@@ -6661,18 +5999,15 @@
       </c>
     </row>
     <row r="331" spans="1:3">
-      <c r="A331" s="1" t="s">
+      <c r="A331" s="3" t="s">
         <v>608</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C331" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="1" t="s">
+      <c r="A332" s="3" t="s">
         <v>610</v>
       </c>
       <c r="B332" s="2" t="s">
@@ -6683,7 +6018,7 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="1" t="s">
+      <c r="A333" s="3" t="s">
         <v>612</v>
       </c>
       <c r="B333" s="2" t="s">
@@ -6694,18 +6029,15 @@
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="1" t="s">
+      <c r="A334" s="3" t="s">
         <v>615</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C334" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="335" spans="1:3">
-      <c r="A335" s="1" t="s">
+      <c r="A335" s="3" t="s">
         <v>616</v>
       </c>
       <c r="B335" s="2" t="s">
@@ -6716,40 +6048,31 @@
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="1" t="s">
+      <c r="A336" s="3" t="s">
         <v>619</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C336" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="1" t="s">
+      <c r="A337" s="3" t="s">
         <v>620</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="C337" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="338" spans="1:3">
-      <c r="A338" s="1" t="s">
+      <c r="A338" s="3" t="s">
         <v>622</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C338" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="339" spans="1:3">
-      <c r="A339" s="1" t="s">
+      <c r="A339" s="3" t="s">
         <v>624</v>
       </c>
       <c r="B339" s="2" t="s">
@@ -6760,95 +6083,71 @@
       </c>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="1" t="s">
+      <c r="A340" s="3" t="s">
         <v>625</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C340" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="1" t="s">
+      <c r="A341" s="3" t="s">
         <v>626</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C341" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="1" t="s">
+      <c r="A342" s="3" t="s">
         <v>627</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C342" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="343" spans="1:3">
-      <c r="A343" s="1" t="s">
+      <c r="A343" s="3" t="s">
         <v>629</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C343" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="1" t="s">
+      <c r="A344" s="3" t="s">
         <v>631</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="C344" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="1" t="s">
+      <c r="A345" s="3" t="s">
         <v>633</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C345" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="1" t="s">
+      <c r="A346" s="3" t="s">
         <v>634</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C346" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="347" spans="1:3">
-      <c r="A347" s="1" t="s">
+      <c r="A347" s="3" t="s">
         <v>636</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="C347" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="1" t="s">
+      <c r="A348" s="3" t="s">
         <v>638</v>
       </c>
       <c r="B348" s="2" t="s">
@@ -6859,7 +6158,7 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="1" t="s">
+      <c r="A349" s="3" t="s">
         <v>640</v>
       </c>
       <c r="B349" s="2" t="s">
@@ -6870,62 +6169,47 @@
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="1" t="s">
+      <c r="A350" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C350" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="1" t="s">
+      <c r="A351" s="3" t="s">
         <v>644</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="C351" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="1" t="s">
+      <c r="A352" s="3" t="s">
         <v>646</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C352" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="1" t="s">
+      <c r="A353" s="3" t="s">
         <v>648</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C353" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="354" spans="1:3">
-      <c r="A354" s="1" t="s">
+      <c r="A354" s="3" t="s">
         <v>649</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C354" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="355" spans="1:3">
-      <c r="A355" s="1" t="s">
+      <c r="A355" s="3" t="s">
         <v>651</v>
       </c>
       <c r="B355" s="2" t="s">
@@ -6936,7 +6220,7 @@
       </c>
     </row>
     <row r="356" spans="1:3">
-      <c r="A356" s="1" t="s">
+      <c r="A356" s="3" t="s">
         <v>654</v>
       </c>
       <c r="B356" s="2" t="s">
@@ -6947,18 +6231,15 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="1" t="s">
+      <c r="A357" s="3" t="s">
         <v>657</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="C357" s="2" t="e">
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="1" t="s">
+      <c r="A358" s="3" t="s">
         <v>658</v>
       </c>
       <c r="B358" s="2" t="s">
@@ -6969,8 +6250,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>